--- a/proposal/H2_results.xlsx
+++ b/proposal/H2_results.xlsx
@@ -1296,7 +1296,7 @@
       </c>
       <c r="C17" s="27" t="inlineStr">
         <is>
-          <t>d(Q,GT) ≈ 0.22 avg  vs  d(C,GT) ≈ 0.10  and  d(Q,C) ≈ 0.18. Queries sit noticeably further from their relevant documents.</t>
+          <t>d(Q,GT) ≈ 0.17 avg  vs  d(C,GT) ≈ 0.10  and  d(Q,C) ≈ 0.17. Queries sit noticeably further from their relevant documents.</t>
         </is>
       </c>
     </row>
@@ -11968,7 +11968,7 @@
       </c>
       <c r="E6" s="83" t="inlineStr">
         <is>
-          <t>Top-1 = 17.9%   Avg. GT Rank = 17.6
+          <t>Top-1 = 14.8%   Avg. GT Rank = 9.87
 Worst overall. Centroid is not a reliable proxy for the query.</t>
         </is>
       </c>
